--- a/MAJSushiConfig/ig/StructureDefinition-fr-actor-extension.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-fr-actor-extension.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-actor-extension</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:09:50+00:00</t>
+    <t>2026-09-07T10:25:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -377,7 +377,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/document-core/ValueSet/fr-vs-actor-type-document|0.1.0</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -433,7 +433,7 @@
     <t>Extension.extension:actor.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|Device|4.0.1|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-organization-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/fhir-document-core/StructureDefinition/fr-patient-document|0.1.0)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-practitionerRole-document|0.1.0|Device|4.0.1|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-device-auteur-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-organization-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-related-person-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-ins-document|0.1.0|https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-patient-document|0.1.0)
 </t>
   </si>
   <si>
@@ -776,7 +776,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="78.171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="74.97265625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
